--- a/assessment_forms/010_vertical_band_saw_skills_assessment--assessment_forms.xlsx
+++ b/assessment_forms/010_vertical_band_saw_skills_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hand-held</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hand-held</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blade_setting_method_choices</t>
+          <t>saw_stop_method_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>automatic</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>saw_stop_method_choices</t>
+          <t>cut_length_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cut_length_choices</t>
+          <t>cut_orientation_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Straight</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>angle</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Straight</t>
+          <t>Angle</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cut_orientation_choices</t>
+          <t>saw_alignment_method_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>angle</t>
+          <t>by_hand</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>By Hand</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>by_hand</t>
+          <t>by_eye</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>By Hand</t>
+          <t>By Eye</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>saw_alignment_method_choices</t>
+          <t>saw_stopping_method_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>by_eye</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>By Eye</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>automatic</t>
+          <t>by_hand</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Automatic</t>
+          <t>By Hand</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>saw_stopping_method_choices</t>
+          <t>cut_direction_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>by_hand</t>
+          <t>with_the_grain</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>By Hand</t>
+          <t>With the grain</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>with_the_grain</t>
+          <t>against_the_grain</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>With the grain</t>
+          <t>Against the grain</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cut_direction_choices</t>
+          <t>blade_alignment_check_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>against_the_grain</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Against the grain</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>blade_alignment_check_choices</t>
+          <t>cutting_dust_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cutting_dust_choices</t>
+          <t>blade_setting_check_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>blade_setting_check_choices</t>
+          <t>saw_support_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>saw_support_choices</t>
+          <t>safety_guards_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>safety_guards_choices</t>
+          <t>cut_location_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>on_top</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>On top</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>on_top</t>
+          <t>on_the_back</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>On top</t>
+          <t>On the back</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>on_the_back</t>
+          <t>below_the_band</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>On the back</t>
+          <t>Below the band</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cut_location_choices</t>
+          <t>blade_angle_check_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>below_the_band</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Below the band</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1981,29 +1981,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>blade_angle_check_choices</t>
+          <t>saw_alignment_check_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2032,29 +2032,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>saw_alignment_check_choices</t>
+          <t>saw_stop_check_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2083,27 +2083,10 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
-        <is>
-          <t>Occasionally</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>saw_stop_check_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
